--- a/Fill Series.xlsx
+++ b/Fill Series.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A38E0A67-466A-4F72-92AD-DB6AF427624C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417010ED-D38C-483F-B434-64B1D46DE24D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{37241379-0B97-4323-A7CF-2BE0773DA4FE}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="63">
   <si>
     <t>Linear</t>
   </si>
@@ -196,6 +196,33 @@
   </si>
   <si>
     <t>just</t>
+  </si>
+  <si>
+    <t>go to files</t>
+  </si>
+  <si>
+    <t>click option</t>
+  </si>
+  <si>
+    <t>click advanced</t>
+  </si>
+  <si>
+    <t>scroll dowun to botton of advanced</t>
+  </si>
+  <si>
+    <t>edit custom list</t>
+  </si>
+  <si>
+    <t>select the required text or series</t>
+  </si>
+  <si>
+    <t>then click add</t>
+  </si>
+  <si>
+    <t>then click ok</t>
+  </si>
+  <si>
+    <t>click of</t>
   </si>
 </sst>
 </file>
@@ -554,7 +581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E7F5DCC-BFD6-499D-A937-875EAE371A7D}">
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.90625" bestFit="1" customWidth="1"/>
@@ -567,6 +594,7 @@
     <col min="8" max="8" width="27.08984375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="24.1796875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="30.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.35">
@@ -1008,17 +1036,23 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="M17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="M18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>13</v>
       </c>
@@ -1040,8 +1074,11 @@
       <c r="J19" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="M19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>17</v>
       </c>
@@ -1063,8 +1100,11 @@
       <c r="J20" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="M20" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>23</v>
       </c>
@@ -1077,8 +1117,11 @@
       <c r="H21" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="M21" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>25</v>
       </c>
@@ -1090,6 +1133,24 @@
       </c>
       <c r="H22" t="s">
         <v>25</v>
+      </c>
+      <c r="M22" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="M23" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="M24" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="M25" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
